--- a/artfynd/A 46621-2022 artfynd.xlsx
+++ b/artfynd/A 46621-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46621-2022 artfynd.xlsx
+++ b/artfynd/A 46621-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96052182</v>
+        <v>96052165</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +709,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ursåsen, Jmt</t>
+          <t>ursåsen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534057.5400597885</v>
+        <v>534067</v>
       </c>
       <c r="R2" t="n">
-        <v>7100844.371959482</v>
+        <v>7100841</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2021-09-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,37 +780,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96052165</v>
+        <v>88629512</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,14 +814,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>ursåsen, Jmt</t>
+          <t>Ursbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534066.3506682464</v>
+        <v>534080</v>
       </c>
       <c r="R3" t="n">
-        <v>7100841.399986153</v>
+        <v>7100951</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,22 +848,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,6 +878,221 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>96052182</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ursåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>534057</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7100844</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-09-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-09-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>96052114</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ursåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>534064</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7101126</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-09-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-09-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>jamande och ivägflygande</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 46621-2022 artfynd.xlsx
+++ b/artfynd/A 46621-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96052165</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88629512</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96052182</t>
         </is>
       </c>
     </row>
@@ -1097,8 +1117,19 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96052114</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>